--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_9.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_9.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:M155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,3545 +469,6960 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:11.948</t>
+          <t>2026-05-29 09:37:28.955</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779421814069</v>
+        <v>1780022247062</v>
       </c>
       <c r="C2" t="n">
-        <v>86072</v>
+        <v>86386</v>
       </c>
       <c r="D2" t="n">
-        <v>16533.86</v>
+        <v>1735.59</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F2" t="n">
-        <v>805</v>
+        <v>1319</v>
       </c>
       <c r="G2" t="n">
-        <v>113.71</v>
+        <v>312.26</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1892</v>
+      </c>
+      <c r="L2" t="n">
+        <v>109</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.112</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:12.367</t>
+          <t>2026-05-29 09:37:28.957</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779421814270</v>
+        <v>1780022247262</v>
       </c>
       <c r="C3" t="n">
-        <v>85573</v>
+        <v>82640</v>
       </c>
       <c r="D3" t="n">
-        <v>15208.17</v>
+        <v>-2097.19</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F3" t="n">
-        <v>805</v>
+        <v>1319</v>
       </c>
       <c r="G3" t="n">
-        <v>113.71</v>
+        <v>312.26</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1694</v>
+      </c>
+      <c r="L3" t="n">
+        <v>111</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:12.368</t>
+          <t>2026-05-29 09:37:29.143</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779421814472</v>
+        <v>1780022247462</v>
       </c>
       <c r="C4" t="n">
-        <v>85817</v>
+        <v>79055</v>
       </c>
       <c r="D4" t="n">
-        <v>14691.76</v>
+        <v>-5577.33</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F4" t="n">
-        <v>805</v>
+        <v>1319</v>
       </c>
       <c r="G4" t="n">
-        <v>113.71</v>
+        <v>312.26</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1680</v>
+      </c>
+      <c r="L4" t="n">
+        <v>114</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.908</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:12.559</t>
+          <t>2026-05-29 09:37:29.162</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779421814673</v>
+        <v>1780022247662</v>
       </c>
       <c r="C5" t="n">
-        <v>86044</v>
+        <v>79837</v>
       </c>
       <c r="D5" t="n">
-        <v>14184.17</v>
+        <v>-4516.46</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="F5" t="n">
-        <v>685</v>
+        <v>1319</v>
       </c>
       <c r="G5" t="n">
-        <v>113.18</v>
+        <v>312.26</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1498</v>
+      </c>
+      <c r="L5" t="n">
+        <v>109</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:12.997</t>
+          <t>2026-05-29 09:37:29.164</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779421814875</v>
+        <v>1780022247881</v>
       </c>
       <c r="C6" t="n">
-        <v>86231</v>
+        <v>82369</v>
       </c>
       <c r="D6" t="n">
-        <v>13661.96</v>
+        <v>-1758.64</v>
       </c>
       <c r="E6" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
-        <v>685</v>
+        <v>1319</v>
       </c>
       <c r="G6" t="n">
-        <v>113.18</v>
+        <v>312.26</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1281</v>
+      </c>
+      <c r="L6" t="n">
+        <v>110</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.101</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:13.000</t>
+          <t>2026-05-29 09:37:29.165</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779421815076</v>
+        <v>1780022248081</v>
       </c>
       <c r="C7" t="n">
-        <v>85681</v>
+        <v>83859</v>
       </c>
       <c r="D7" t="n">
-        <v>12428.87</v>
+        <v>-180.71</v>
       </c>
       <c r="E7" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
-        <v>685</v>
+        <v>1319</v>
       </c>
       <c r="G7" t="n">
-        <v>113.18</v>
+        <v>312.26</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1083</v>
+      </c>
+      <c r="L7" t="n">
+        <v>111</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.948</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:14.424</t>
+          <t>2026-05-29 09:37:29.374</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779421815277</v>
+        <v>1780022248281</v>
       </c>
       <c r="C8" t="n">
-        <v>85824</v>
+        <v>84696</v>
       </c>
       <c r="D8" t="n">
-        <v>11950.42</v>
+        <v>665.33</v>
       </c>
       <c r="E8" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="F8" t="n">
-        <v>685</v>
+        <v>1319</v>
       </c>
       <c r="G8" t="n">
-        <v>113.18</v>
+        <v>312.26</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1093</v>
+      </c>
+      <c r="L8" t="n">
+        <v>116</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.893</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:14.464</t>
+          <t>2026-05-29 09:37:29.376</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779421815479</v>
+        <v>1780022248481</v>
       </c>
       <c r="C9" t="n">
-        <v>85994</v>
+        <v>84561</v>
       </c>
       <c r="D9" t="n">
-        <v>11522.9</v>
+        <v>497.06</v>
       </c>
       <c r="E9" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="F9" t="n">
-        <v>685</v>
+        <v>1319</v>
       </c>
       <c r="G9" t="n">
-        <v>113.18</v>
+        <v>312.26</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K9" t="n">
+        <v>894</v>
+      </c>
+      <c r="L9" t="n">
+        <v>110</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:14.465</t>
+          <t>2026-05-29 09:37:30.413</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779421815680</v>
+        <v>1780022248681</v>
       </c>
       <c r="C10" t="n">
-        <v>86180</v>
+        <v>83924</v>
       </c>
       <c r="D10" t="n">
-        <v>11132.76</v>
+        <v>-164.79</v>
       </c>
       <c r="E10" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F10" t="n">
-        <v>926</v>
+        <v>1319</v>
       </c>
       <c r="G10" t="n">
-        <v>109.38</v>
+        <v>312.26</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1731</v>
+      </c>
+      <c r="L10" t="n">
+        <v>119</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.926</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:14.465</t>
+          <t>2026-05-29 09:37:30.430</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779421815882</v>
+        <v>1780022248881</v>
       </c>
       <c r="C11" t="n">
-        <v>85532</v>
+        <v>84413</v>
       </c>
       <c r="D11" t="n">
-        <v>9928.120000000001</v>
+        <v>332.45</v>
       </c>
       <c r="E11" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F11" t="n">
-        <v>926</v>
+        <v>1319</v>
       </c>
       <c r="G11" t="n">
-        <v>109.38</v>
+        <v>312.26</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1548</v>
+      </c>
+      <c r="L11" t="n">
+        <v>119</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.841</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:14.466</t>
+          <t>2026-05-29 09:37:30.637</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779421816083</v>
+        <v>1780022249081</v>
       </c>
       <c r="C12" t="n">
-        <v>85725</v>
+        <v>83800</v>
       </c>
       <c r="D12" t="n">
-        <v>9624.709999999999</v>
+        <v>-297.18</v>
       </c>
       <c r="E12" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>926</v>
+        <v>1319</v>
       </c>
       <c r="G12" t="n">
-        <v>109.38</v>
+        <v>312.26</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1555</v>
+      </c>
+      <c r="L12" t="n">
+        <v>106</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.143</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:14.467</t>
+          <t>2026-05-29 09:37:30.639</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779421816284</v>
+        <v>1780022249281</v>
       </c>
       <c r="C13" t="n">
-        <v>85862</v>
+        <v>84360</v>
       </c>
       <c r="D13" t="n">
-        <v>9280.48</v>
+        <v>277.68</v>
       </c>
       <c r="E13" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F13" t="n">
-        <v>926</v>
+        <v>1319</v>
       </c>
       <c r="G13" t="n">
-        <v>109.38</v>
+        <v>312.26</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1357</v>
+      </c>
+      <c r="L13" t="n">
+        <v>120</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.318</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:14.610</t>
+          <t>2026-05-29 09:37:30.649</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779421816486</v>
+        <v>1780022249481</v>
       </c>
       <c r="C14" t="n">
-        <v>86019</v>
+        <v>85425</v>
       </c>
       <c r="D14" t="n">
-        <v>8973.450000000001</v>
+        <v>1328.8</v>
       </c>
       <c r="E14" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F14" t="n">
-        <v>846</v>
+        <v>1319</v>
       </c>
       <c r="G14" t="n">
-        <v>104.27</v>
+        <v>312.26</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1167</v>
+      </c>
+      <c r="L14" t="n">
+        <v>109</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.709</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:14.611</t>
+          <t>2026-05-29 09:37:30.700</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779421816687</v>
+        <v>1780022249700</v>
       </c>
       <c r="C15" t="n">
-        <v>85557</v>
+        <v>85122</v>
       </c>
       <c r="D15" t="n">
-        <v>8062.78</v>
+        <v>959.36</v>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F15" t="n">
-        <v>846</v>
+        <v>1319</v>
       </c>
       <c r="G15" t="n">
-        <v>104.27</v>
+        <v>312.26</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>107</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:15.098</t>
+          <t>2026-05-29 09:37:31.128</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779421816889</v>
+        <v>1780022249901</v>
       </c>
       <c r="C16" t="n">
-        <v>85790</v>
+        <v>85521</v>
       </c>
       <c r="D16" t="n">
-        <v>7892.64</v>
+        <v>1310.39</v>
       </c>
       <c r="E16" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F16" t="n">
-        <v>846</v>
+        <v>1319</v>
       </c>
       <c r="G16" t="n">
-        <v>104.27</v>
+        <v>312.26</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1225</v>
+      </c>
+      <c r="L16" t="n">
+        <v>134</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:15.122</t>
+          <t>2026-05-29 09:37:31.159</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779421817090</v>
+        <v>1780022250100</v>
       </c>
       <c r="C17" t="n">
-        <v>86006</v>
+        <v>84979</v>
       </c>
       <c r="D17" t="n">
-        <v>7714.01</v>
+        <v>702.87</v>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F17" t="n">
-        <v>846</v>
+        <v>1319</v>
       </c>
       <c r="G17" t="n">
-        <v>104.27</v>
+        <v>312.26</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1058</v>
+      </c>
+      <c r="L17" t="n">
+        <v>106</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:15.123</t>
+          <t>2026-05-29 09:37:31.555</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779421817291</v>
+        <v>1780022250300</v>
       </c>
       <c r="C18" t="n">
-        <v>86111</v>
+        <v>84897</v>
       </c>
       <c r="D18" t="n">
-        <v>7433.31</v>
+        <v>585.73</v>
       </c>
       <c r="E18" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F18" t="n">
-        <v>685</v>
+        <v>1319</v>
       </c>
       <c r="G18" t="n">
-        <v>105.23</v>
+        <v>312.26</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1254</v>
+      </c>
+      <c r="L18" t="n">
+        <v>114</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.884</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:15.447</t>
+          <t>2026-05-29 09:37:31.556</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779421817493</v>
+        <v>1780022250500</v>
       </c>
       <c r="C19" t="n">
-        <v>85624</v>
+        <v>85737</v>
       </c>
       <c r="D19" t="n">
-        <v>6574.64</v>
+        <v>1396.44</v>
       </c>
       <c r="E19" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F19" t="n">
-        <v>685</v>
+        <v>1319</v>
       </c>
       <c r="G19" t="n">
-        <v>105.23</v>
+        <v>312.26</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1055</v>
+      </c>
+      <c r="L19" t="n">
+        <v>113</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.929</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:15.457</t>
+          <t>2026-05-29 09:37:31.964</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779421817694</v>
+        <v>1780022250700</v>
       </c>
       <c r="C20" t="n">
-        <v>85836</v>
+        <v>86559</v>
       </c>
       <c r="D20" t="n">
-        <v>6457.91</v>
+        <v>2148.62</v>
       </c>
       <c r="E20" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F20" t="n">
-        <v>685</v>
+        <v>5117</v>
       </c>
       <c r="G20" t="n">
-        <v>105.23</v>
+        <v>312.26</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1263</v>
+      </c>
+      <c r="L20" t="n">
+        <v>117</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.774</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:15.845</t>
+          <t>2026-05-29 09:37:31.998</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779421817896</v>
+        <v>1780022250900</v>
       </c>
       <c r="C21" t="n">
-        <v>86046</v>
+        <v>86514</v>
       </c>
       <c r="D21" t="n">
-        <v>6345.02</v>
+        <v>1996.19</v>
       </c>
       <c r="E21" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F21" t="n">
-        <v>765</v>
+        <v>5117</v>
       </c>
       <c r="G21" t="n">
-        <v>90.06</v>
+        <v>312.26</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1096</v>
+      </c>
+      <c r="L21" t="n">
+        <v>116</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:15.847</t>
+          <t>2026-05-29 09:37:32.229</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779421818097</v>
+        <v>1780022251100</v>
       </c>
       <c r="C22" t="n">
-        <v>85608</v>
+        <v>86600</v>
       </c>
       <c r="D22" t="n">
-        <v>5589.77</v>
+        <v>1982.38</v>
       </c>
       <c r="E22" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F22" t="n">
-        <v>765</v>
+        <v>5117</v>
       </c>
       <c r="G22" t="n">
-        <v>90.06</v>
+        <v>312.26</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1128</v>
+      </c>
+      <c r="L22" t="n">
+        <v>115</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.913</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:16.247</t>
+          <t>2026-05-29 09:37:32.242</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779421818298</v>
+        <v>1780022251300</v>
       </c>
       <c r="C23" t="n">
-        <v>85657</v>
+        <v>86727</v>
       </c>
       <c r="D23" t="n">
-        <v>5359.28</v>
+        <v>2010.26</v>
       </c>
       <c r="E23" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F23" t="n">
-        <v>765</v>
+        <v>5117</v>
       </c>
       <c r="G23" t="n">
-        <v>90.06</v>
+        <v>312.26</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K23" t="n">
+        <v>941</v>
+      </c>
+      <c r="L23" t="n">
+        <v>122</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.904</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:16.248</t>
+          <t>2026-05-29 09:37:32.780</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779421818500</v>
+        <v>1780022251519</v>
       </c>
       <c r="C24" t="n">
-        <v>85831</v>
+        <v>86727</v>
       </c>
       <c r="D24" t="n">
-        <v>5265.31</v>
+        <v>1909.75</v>
       </c>
       <c r="E24" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F24" t="n">
-        <v>765</v>
+        <v>5117</v>
       </c>
       <c r="G24" t="n">
-        <v>90.06</v>
+        <v>312.26</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1259</v>
+      </c>
+      <c r="L24" t="n">
+        <v>115</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.536</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:16.665</t>
+          <t>2026-05-29 09:37:32.781</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779421818701</v>
+        <v>1780022251719</v>
       </c>
       <c r="C25" t="n">
-        <v>86041</v>
+        <v>86977</v>
       </c>
       <c r="D25" t="n">
-        <v>5212.05</v>
+        <v>2064.26</v>
       </c>
       <c r="E25" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F25" t="n">
-        <v>766</v>
+        <v>5117</v>
       </c>
       <c r="G25" t="n">
-        <v>89.98999999999999</v>
+        <v>312.26</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1061</v>
+      </c>
+      <c r="L25" t="n">
+        <v>120</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.534</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:16.666</t>
+          <t>2026-05-29 09:37:32.788</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779421818903</v>
+        <v>1780022251919</v>
       </c>
       <c r="C26" t="n">
-        <v>85517</v>
+        <v>87309</v>
       </c>
       <c r="D26" t="n">
-        <v>4427.44</v>
+        <v>2293.05</v>
       </c>
       <c r="E26" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F26" t="n">
-        <v>766</v>
+        <v>5117</v>
       </c>
       <c r="G26" t="n">
-        <v>89.98999999999999</v>
+        <v>312.26</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K26" t="n">
+        <v>868</v>
+      </c>
+      <c r="L26" t="n">
+        <v>109</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:17.114</t>
+          <t>2026-05-29 09:37:33.139</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779421819104</v>
+        <v>1780022252119</v>
       </c>
       <c r="C27" t="n">
-        <v>85665</v>
+        <v>87193</v>
       </c>
       <c r="D27" t="n">
-        <v>4354.07</v>
+        <v>2062.39</v>
       </c>
       <c r="E27" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F27" t="n">
-        <v>766</v>
+        <v>5117</v>
       </c>
       <c r="G27" t="n">
-        <v>89.98999999999999</v>
+        <v>312.26</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1018</v>
+      </c>
+      <c r="L27" t="n">
+        <v>114</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.579</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:17.131</t>
+          <t>2026-05-29 09:37:33.458</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779421819305</v>
+        <v>1780022252320</v>
       </c>
       <c r="C28" t="n">
-        <v>85885</v>
+        <v>87320</v>
       </c>
       <c r="D28" t="n">
-        <v>4356.37</v>
+        <v>2086.27</v>
       </c>
       <c r="E28" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F28" t="n">
-        <v>766</v>
+        <v>5117</v>
       </c>
       <c r="G28" t="n">
-        <v>89.98999999999999</v>
+        <v>312.26</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1137</v>
+      </c>
+      <c r="L28" t="n">
+        <v>108</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.138</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:17.482</t>
+          <t>2026-05-29 09:37:33.460</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779421819507</v>
+        <v>1780022252519</v>
       </c>
       <c r="C29" t="n">
-        <v>86077</v>
+        <v>87447</v>
       </c>
       <c r="D29" t="n">
-        <v>4330.55</v>
+        <v>2108.96</v>
       </c>
       <c r="E29" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F29" t="n">
-        <v>765</v>
+        <v>5117</v>
       </c>
       <c r="G29" t="n">
-        <v>89.86</v>
+        <v>312.26</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K29" t="n">
+        <v>940</v>
+      </c>
+      <c r="L29" t="n">
+        <v>142</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.164</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:17.482</t>
+          <t>2026-05-29 09:37:33.932</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779421819708</v>
+        <v>1780022252720</v>
       </c>
       <c r="C30" t="n">
-        <v>85652</v>
+        <v>87501</v>
       </c>
       <c r="D30" t="n">
-        <v>3689.02</v>
+        <v>2057.51</v>
       </c>
       <c r="E30" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F30" t="n">
-        <v>765</v>
+        <v>5117</v>
       </c>
       <c r="G30" t="n">
-        <v>89.86</v>
+        <v>312.26</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1211</v>
+      </c>
+      <c r="L30" t="n">
+        <v>108</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.143</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:17.906</t>
+          <t>2026-05-29 09:37:33.948</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779421819910</v>
+        <v>1780022252919</v>
       </c>
       <c r="C31" t="n">
-        <v>85812</v>
+        <v>87801</v>
       </c>
       <c r="D31" t="n">
-        <v>3664.57</v>
+        <v>2254.64</v>
       </c>
       <c r="E31" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F31" t="n">
-        <v>765</v>
+        <v>5117</v>
       </c>
       <c r="G31" t="n">
-        <v>89.86</v>
+        <v>312.26</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1028</v>
+      </c>
+      <c r="L31" t="n">
+        <v>118</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.914</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:17.935</t>
+          <t>2026-05-29 09:37:34.955</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779421820111</v>
+        <v>1780022253139</v>
       </c>
       <c r="C32" t="n">
-        <v>86033</v>
+        <v>87745</v>
       </c>
       <c r="D32" t="n">
-        <v>3702.34</v>
+        <v>2085.91</v>
       </c>
       <c r="E32" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F32" t="n">
-        <v>685</v>
+        <v>5117</v>
       </c>
       <c r="G32" t="n">
-        <v>92.98</v>
+        <v>312.26</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1815</v>
+      </c>
+      <c r="L32" t="n">
+        <v>113</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.307</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:18.302</t>
+          <t>2026-05-29 09:37:34.976</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779421820313</v>
+        <v>1780022253358</v>
       </c>
       <c r="C33" t="n">
-        <v>85678</v>
+        <v>87308</v>
       </c>
       <c r="D33" t="n">
-        <v>3162.23</v>
+        <v>1544.61</v>
       </c>
       <c r="E33" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F33" t="n">
-        <v>685</v>
+        <v>5117</v>
       </c>
       <c r="G33" t="n">
-        <v>92.98</v>
+        <v>312.26</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1617</v>
+      </c>
+      <c r="L33" t="n">
+        <v>111</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.092</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:18.302</t>
+          <t>2026-05-29 09:37:34.978</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779421820514</v>
+        <v>1780022253558</v>
       </c>
       <c r="C34" t="n">
-        <v>85720</v>
+        <v>87180</v>
       </c>
       <c r="D34" t="n">
-        <v>3046.11</v>
+        <v>1339.38</v>
       </c>
       <c r="E34" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F34" t="n">
-        <v>685</v>
+        <v>5117</v>
       </c>
       <c r="G34" t="n">
-        <v>92.98</v>
+        <v>312.26</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1419</v>
+      </c>
+      <c r="L34" t="n">
+        <v>109</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.124</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:18.819</t>
+          <t>2026-05-29 09:37:35.124</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779421820715</v>
+        <v>1780022253758</v>
       </c>
       <c r="C35" t="n">
-        <v>85948</v>
+        <v>87457</v>
       </c>
       <c r="D35" t="n">
-        <v>3121.81</v>
+        <v>1549.41</v>
       </c>
       <c r="E35" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F35" t="n">
-        <v>685</v>
+        <v>5117</v>
       </c>
       <c r="G35" t="n">
-        <v>92.98</v>
+        <v>312.26</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1365</v>
+      </c>
+      <c r="L35" t="n">
+        <v>116</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:18.820</t>
+          <t>2026-05-29 09:37:35.125</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779421820917</v>
+        <v>1780022253958</v>
       </c>
       <c r="C36" t="n">
-        <v>86233</v>
+        <v>87116</v>
       </c>
       <c r="D36" t="n">
-        <v>3250.72</v>
+        <v>1130.94</v>
       </c>
       <c r="E36" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F36" t="n">
-        <v>725</v>
+        <v>5117</v>
       </c>
       <c r="G36" t="n">
-        <v>78.09</v>
+        <v>312.26</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1166</v>
+      </c>
+      <c r="L36" t="n">
+        <v>118</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:19.012</t>
+          <t>2026-05-29 09:37:35.127</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779421821118</v>
+        <v>1780022254158</v>
       </c>
       <c r="C37" t="n">
-        <v>85773</v>
+        <v>87398</v>
       </c>
       <c r="D37" t="n">
-        <v>2628.18</v>
+        <v>1356.39</v>
       </c>
       <c r="E37" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F37" t="n">
-        <v>725</v>
+        <v>5117</v>
       </c>
       <c r="G37" t="n">
-        <v>78.09</v>
+        <v>312.26</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K37" t="n">
+        <v>967</v>
+      </c>
+      <c r="L37" t="n">
+        <v>99</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.235</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:19.327</t>
+          <t>2026-05-29 09:37:35.506</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779421821320</v>
+        <v>1780022254359</v>
       </c>
       <c r="C38" t="n">
-        <v>85916</v>
+        <v>87594</v>
       </c>
       <c r="D38" t="n">
-        <v>2639.77</v>
+        <v>1484.57</v>
       </c>
       <c r="E38" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F38" t="n">
-        <v>725</v>
+        <v>3738</v>
       </c>
       <c r="G38" t="n">
-        <v>78.09</v>
+        <v>312.26</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1146</v>
+      </c>
+      <c r="L38" t="n">
+        <v>107</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.978</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:19.328</t>
+          <t>2026-05-29 09:37:35.508</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779421821521</v>
+        <v>1780022254558</v>
       </c>
       <c r="C39" t="n">
-        <v>86106</v>
+        <v>87556</v>
       </c>
       <c r="D39" t="n">
-        <v>2697.78</v>
+        <v>1372.34</v>
       </c>
       <c r="E39" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F39" t="n">
-        <v>725</v>
+        <v>3738</v>
       </c>
       <c r="G39" t="n">
-        <v>78.09</v>
+        <v>312.26</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K39" t="n">
+        <v>949</v>
+      </c>
+      <c r="L39" t="n">
+        <v>122</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.036</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:19.722</t>
+          <t>2026-05-29 09:37:36.301</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779421821722</v>
+        <v>1780022254759</v>
       </c>
       <c r="C40" t="n">
-        <v>86307</v>
+        <v>87771</v>
       </c>
       <c r="D40" t="n">
-        <v>2763.9</v>
+        <v>1518.73</v>
       </c>
       <c r="E40" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F40" t="n">
-        <v>786</v>
+        <v>3738</v>
       </c>
       <c r="G40" t="n">
-        <v>77.23999999999999</v>
+        <v>312.26</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1541</v>
+      </c>
+      <c r="L40" t="n">
+        <v>130</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.075</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:19.730</t>
+          <t>2026-05-29 09:37:36.303</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779421821924</v>
+        <v>1780022254977</v>
       </c>
       <c r="C41" t="n">
-        <v>85703</v>
+        <v>88129</v>
       </c>
       <c r="D41" t="n">
-        <v>2021.7</v>
+        <v>1800.79</v>
       </c>
       <c r="E41" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F41" t="n">
-        <v>786</v>
+        <v>3738</v>
       </c>
       <c r="G41" t="n">
-        <v>77.23999999999999</v>
+        <v>312.26</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L41" t="n">
+        <v>121</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.897</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:20.140</t>
+          <t>2026-05-29 09:37:36.319</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779421822125</v>
+        <v>1780022255177</v>
       </c>
       <c r="C42" t="n">
-        <v>85925</v>
+        <v>87855</v>
       </c>
       <c r="D42" t="n">
-        <v>2142.62</v>
+        <v>1436.75</v>
       </c>
       <c r="E42" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F42" t="n">
-        <v>786</v>
+        <v>3738</v>
       </c>
       <c r="G42" t="n">
-        <v>77.23999999999999</v>
+        <v>312.26</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L42" t="n">
+        <v>107</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.385</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:20.141</t>
+          <t>2026-05-29 09:37:36.320</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779421822327</v>
+        <v>1780022255378</v>
       </c>
       <c r="C43" t="n">
-        <v>86131</v>
+        <v>87430</v>
       </c>
       <c r="D43" t="n">
-        <v>2241.49</v>
+        <v>939.91</v>
       </c>
       <c r="E43" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F43" t="n">
-        <v>786</v>
+        <v>3738</v>
       </c>
       <c r="G43" t="n">
-        <v>77.23999999999999</v>
+        <v>312.26</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K43" t="n">
+        <v>941</v>
+      </c>
+      <c r="L43" t="n">
+        <v>107</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.826</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:20.544</t>
+          <t>2026-05-29 09:37:36.550</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779421822528</v>
+        <v>1780022255577</v>
       </c>
       <c r="C44" t="n">
-        <v>86317</v>
+        <v>87173</v>
       </c>
       <c r="D44" t="n">
-        <v>2315.41</v>
+        <v>635.92</v>
       </c>
       <c r="E44" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="F44" t="n">
-        <v>825</v>
+        <v>3738</v>
       </c>
       <c r="G44" t="n">
-        <v>74.08</v>
+        <v>312.26</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K44" t="n">
+        <v>972</v>
+      </c>
+      <c r="L44" t="n">
+        <v>113</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.033</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:20.545</t>
+          <t>2026-05-29 09:37:36.561</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779421822730</v>
+        <v>1780022255777</v>
       </c>
       <c r="C45" t="n">
-        <v>85830</v>
+        <v>87120</v>
       </c>
       <c r="D45" t="n">
-        <v>1712.64</v>
+        <v>551.12</v>
       </c>
       <c r="E45" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="F45" t="n">
-        <v>825</v>
+        <v>3738</v>
       </c>
       <c r="G45" t="n">
-        <v>74.08</v>
+        <v>312.26</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K45" t="n">
+        <v>784</v>
+      </c>
+      <c r="L45" t="n">
+        <v>105</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.484</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:21.028</t>
+          <t>2026-05-29 09:37:36.905</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779421822931</v>
+        <v>1780022255977</v>
       </c>
       <c r="C46" t="n">
-        <v>86007</v>
+        <v>86997</v>
       </c>
       <c r="D46" t="n">
-        <v>1804.01</v>
+        <v>400.57</v>
       </c>
       <c r="E46" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="F46" t="n">
-        <v>825</v>
+        <v>3738</v>
       </c>
       <c r="G46" t="n">
-        <v>74.08</v>
+        <v>312.26</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K46" t="n">
+        <v>926</v>
+      </c>
+      <c r="L46" t="n">
+        <v>114</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:21.029</t>
+          <t>2026-05-29 09:37:36.906</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779421823132</v>
+        <v>1780022256177</v>
       </c>
       <c r="C47" t="n">
-        <v>86294</v>
+        <v>86592</v>
       </c>
       <c r="D47" t="n">
-        <v>2000.81</v>
+        <v>-24.46</v>
       </c>
       <c r="E47" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F47" t="n">
-        <v>705</v>
+        <v>3738</v>
       </c>
       <c r="G47" t="n">
-        <v>55.44</v>
+        <v>312.26</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K47" t="n">
+        <v>728</v>
+      </c>
+      <c r="L47" t="n">
+        <v>109</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.215</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:21.261</t>
+          <t>2026-05-29 09:37:37.446</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779421823334</v>
+        <v>1780022256377</v>
       </c>
       <c r="C48" t="n">
-        <v>86150</v>
+        <v>86807</v>
       </c>
       <c r="D48" t="n">
-        <v>1756.77</v>
+        <v>191.76</v>
       </c>
       <c r="E48" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F48" t="n">
-        <v>705</v>
+        <v>3738</v>
       </c>
       <c r="G48" t="n">
-        <v>55.44</v>
+        <v>312.26</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1068</v>
+      </c>
+      <c r="L48" t="n">
+        <v>116</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.711</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:21.262</t>
+          <t>2026-05-29 09:37:37.467</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779421823535</v>
+        <v>1780022256577</v>
       </c>
       <c r="C49" t="n">
-        <v>86021</v>
+        <v>86362</v>
       </c>
       <c r="D49" t="n">
-        <v>1539.93</v>
+        <v>-262.83</v>
       </c>
       <c r="E49" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F49" t="n">
-        <v>705</v>
+        <v>3738</v>
       </c>
       <c r="G49" t="n">
-        <v>55.44</v>
+        <v>312.26</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K49" t="n">
+        <v>889</v>
+      </c>
+      <c r="L49" t="n">
+        <v>115</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.951</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:21.590</t>
+          <t>2026-05-29 09:37:37.726</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779421823737</v>
+        <v>1780022256796</v>
       </c>
       <c r="C50" t="n">
-        <v>86219</v>
+        <v>86503</v>
       </c>
       <c r="D50" t="n">
-        <v>1660.93</v>
+        <v>-108.69</v>
       </c>
       <c r="E50" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F50" t="n">
-        <v>705</v>
+        <v>3738</v>
       </c>
       <c r="G50" t="n">
-        <v>55.44</v>
+        <v>312.26</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K50" t="n">
+        <v>929</v>
+      </c>
+      <c r="L50" t="n">
+        <v>114</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.117</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:21.992</t>
+          <t>2026-05-29 09:37:37.870</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779421823938</v>
+        <v>1780022256996</v>
       </c>
       <c r="C51" t="n">
-        <v>86507</v>
+        <v>86662</v>
       </c>
       <c r="D51" t="n">
-        <v>1865.89</v>
+        <v>55.75</v>
       </c>
       <c r="E51" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="F51" t="n">
-        <v>705</v>
+        <v>3738</v>
       </c>
       <c r="G51" t="n">
-        <v>47.11</v>
+        <v>312.26</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K51" t="n">
+        <v>874</v>
+      </c>
+      <c r="L51" t="n">
+        <v>117</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.593</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:21.993</t>
+          <t>2026-05-29 09:37:38.150</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779421824139</v>
+        <v>1780022257196</v>
       </c>
       <c r="C52" t="n">
-        <v>86040</v>
+        <v>86592</v>
       </c>
       <c r="D52" t="n">
-        <v>1305.59</v>
+        <v>-17.04</v>
       </c>
       <c r="E52" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="F52" t="n">
-        <v>705</v>
+        <v>2818</v>
       </c>
       <c r="G52" t="n">
-        <v>47.11</v>
+        <v>312.26</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K52" t="n">
+        <v>953</v>
+      </c>
+      <c r="L52" t="n">
+        <v>114</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.218</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:22.391</t>
+          <t>2026-05-29 09:37:38.151</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779421824341</v>
+        <v>1780022257396</v>
       </c>
       <c r="C53" t="n">
-        <v>86017</v>
+        <v>86761</v>
       </c>
       <c r="D53" t="n">
-        <v>1217.31</v>
+        <v>152.81</v>
       </c>
       <c r="E53" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="F53" t="n">
-        <v>705</v>
+        <v>2818</v>
       </c>
       <c r="G53" t="n">
-        <v>47.11</v>
+        <v>312.26</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K53" t="n">
+        <v>754</v>
+      </c>
+      <c r="L53" t="n">
+        <v>111</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.101</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:22.392</t>
+          <t>2026-05-29 09:37:38.596</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779421824542</v>
+        <v>1780022257596</v>
       </c>
       <c r="C54" t="n">
-        <v>86131</v>
+        <v>86779</v>
       </c>
       <c r="D54" t="n">
-        <v>1270.45</v>
+        <v>163.17</v>
       </c>
       <c r="E54" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="F54" t="n">
-        <v>705</v>
+        <v>2818</v>
       </c>
       <c r="G54" t="n">
-        <v>47.11</v>
+        <v>312.26</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K54" t="n">
+        <v>999</v>
+      </c>
+      <c r="L54" t="n">
+        <v>111</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.246</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:22.802</t>
+          <t>2026-05-29 09:37:38.599</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779421824744</v>
+        <v>1780022257796</v>
       </c>
       <c r="C55" t="n">
-        <v>86290</v>
+        <v>86378</v>
       </c>
       <c r="D55" t="n">
-        <v>1365.92</v>
+        <v>-245.99</v>
       </c>
       <c r="E55" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F55" t="n">
-        <v>907</v>
+        <v>2818</v>
       </c>
       <c r="G55" t="n">
-        <v>66.15000000000001</v>
+        <v>312.26</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K55" t="n">
+        <v>801</v>
+      </c>
+      <c r="L55" t="n">
+        <v>107</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.717</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:22.811</t>
+          <t>2026-05-29 09:37:38.974</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779421824945</v>
+        <v>1780022257996</v>
       </c>
       <c r="C56" t="n">
-        <v>85912</v>
+        <v>86541</v>
       </c>
       <c r="D56" t="n">
-        <v>919.63</v>
+        <v>-70.69</v>
       </c>
       <c r="E56" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F56" t="n">
-        <v>907</v>
+        <v>2818</v>
       </c>
       <c r="G56" t="n">
-        <v>66.15000000000001</v>
+        <v>312.26</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K56" t="n">
+        <v>977</v>
+      </c>
+      <c r="L56" t="n">
+        <v>114</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.164</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:23.335</t>
+          <t>2026-05-29 09:37:38.976</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779421825146</v>
+        <v>1780022258196</v>
       </c>
       <c r="C57" t="n">
-        <v>86010</v>
+        <v>86568</v>
       </c>
       <c r="D57" t="n">
-        <v>971.65</v>
+        <v>-40.15</v>
       </c>
       <c r="E57" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F57" t="n">
-        <v>907</v>
+        <v>2818</v>
       </c>
       <c r="G57" t="n">
-        <v>66.15000000000001</v>
+        <v>312.26</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K57" t="n">
+        <v>779</v>
+      </c>
+      <c r="L57" t="n">
+        <v>113</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.918</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:23.356</t>
+          <t>2026-05-29 09:37:39.402</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779421825348</v>
+        <v>1780022258396</v>
       </c>
       <c r="C58" t="n">
-        <v>86115</v>
+        <v>86029</v>
       </c>
       <c r="D58" t="n">
-        <v>1028.06</v>
+        <v>-577.14</v>
       </c>
       <c r="E58" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F58" t="n">
-        <v>907</v>
+        <v>1200</v>
       </c>
       <c r="G58" t="n">
-        <v>66.15000000000001</v>
+        <v>323.37</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1006</v>
+      </c>
+      <c r="L58" t="n">
+        <v>115</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.913</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:23.362</t>
+          <t>2026-05-29 09:37:39.424</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779421825549</v>
+        <v>1780022258615</v>
       </c>
       <c r="C59" t="n">
-        <v>86308</v>
+        <v>85371</v>
       </c>
       <c r="D59" t="n">
-        <v>1169.66</v>
+        <v>-1206.29</v>
       </c>
       <c r="E59" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="F59" t="n">
-        <v>765</v>
+        <v>1200</v>
       </c>
       <c r="G59" t="n">
-        <v>66.15000000000001</v>
+        <v>323.37</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K59" t="n">
+        <v>807</v>
+      </c>
+      <c r="L59" t="n">
+        <v>107</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.421</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:23.613</t>
+          <t>2026-05-29 09:37:39.838</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779421825751</v>
+        <v>1780022258815</v>
       </c>
       <c r="C60" t="n">
-        <v>85876</v>
+        <v>85776</v>
       </c>
       <c r="D60" t="n">
-        <v>679.1799999999999</v>
+        <v>-740.97</v>
       </c>
       <c r="E60" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="F60" t="n">
-        <v>765</v>
+        <v>1200</v>
       </c>
       <c r="G60" t="n">
-        <v>66.15000000000001</v>
+        <v>323.37</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1022</v>
+      </c>
+      <c r="L60" t="n">
+        <v>121</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.903</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:24.038</t>
+          <t>2026-05-29 09:37:39.839</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779421825952</v>
+        <v>1780022259015</v>
       </c>
       <c r="C61" t="n">
-        <v>86061</v>
+        <v>86391</v>
       </c>
       <c r="D61" t="n">
-        <v>830.22</v>
+        <v>-88.92</v>
       </c>
       <c r="E61" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="F61" t="n">
-        <v>765</v>
+        <v>1200</v>
       </c>
       <c r="G61" t="n">
-        <v>66.15000000000001</v>
+        <v>323.37</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K61" t="n">
+        <v>823</v>
+      </c>
+      <c r="L61" t="n">
+        <v>108</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.497</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:24.039</t>
+          <t>2026-05-29 09:37:40.208</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779421826153</v>
+        <v>1780022259215</v>
       </c>
       <c r="C62" t="n">
-        <v>86401</v>
+        <v>86602</v>
       </c>
       <c r="D62" t="n">
-        <v>1128.71</v>
+        <v>126.52</v>
       </c>
       <c r="E62" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F62" t="n">
-        <v>644</v>
+        <v>759</v>
       </c>
       <c r="G62" t="n">
-        <v>76.12</v>
+        <v>311.94</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K62" t="n">
+        <v>992</v>
+      </c>
+      <c r="L62" t="n">
+        <v>107</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.438</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:24.462</t>
+          <t>2026-05-29 09:37:40.210</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779421826355</v>
+        <v>1780022259415</v>
       </c>
       <c r="C63" t="n">
-        <v>86428</v>
+        <v>86726</v>
       </c>
       <c r="D63" t="n">
-        <v>1099.27</v>
+        <v>244.2</v>
       </c>
       <c r="E63" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F63" t="n">
-        <v>644</v>
+        <v>759</v>
       </c>
       <c r="G63" t="n">
-        <v>76.12</v>
+        <v>311.94</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K63" t="n">
+        <v>794</v>
+      </c>
+      <c r="L63" t="n">
+        <v>114</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.264</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:24.492</t>
+          <t>2026-05-29 09:37:41.605</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779421826556</v>
+        <v>1780022259615</v>
       </c>
       <c r="C64" t="n">
-        <v>86003</v>
+        <v>86913</v>
       </c>
       <c r="D64" t="n">
-        <v>619.3099999999999</v>
+        <v>418.99</v>
       </c>
       <c r="E64" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F64" t="n">
-        <v>644</v>
+        <v>759</v>
       </c>
       <c r="G64" t="n">
-        <v>76.12</v>
+        <v>311.94</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1989</v>
+      </c>
+      <c r="L64" t="n">
+        <v>111</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.768</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:24.968</t>
+          <t>2026-05-29 09:37:41.614</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779421826758</v>
+        <v>1780022259815</v>
       </c>
       <c r="C65" t="n">
-        <v>86295</v>
+        <v>86810</v>
       </c>
       <c r="D65" t="n">
-        <v>880.34</v>
+        <v>295.04</v>
       </c>
       <c r="E65" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F65" t="n">
-        <v>644</v>
+        <v>759</v>
       </c>
       <c r="G65" t="n">
-        <v>76.12</v>
+        <v>311.94</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1798</v>
+      </c>
+      <c r="L65" t="n">
+        <v>107</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.436</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:24.970</t>
+          <t>2026-05-29 09:37:41.637</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779421826959</v>
+        <v>1780022260015</v>
       </c>
       <c r="C66" t="n">
-        <v>86549</v>
+        <v>86779</v>
       </c>
       <c r="D66" t="n">
-        <v>1090.33</v>
+        <v>249.28</v>
       </c>
       <c r="E66" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F66" t="n">
-        <v>726</v>
+        <v>759</v>
       </c>
       <c r="G66" t="n">
-        <v>76.33</v>
+        <v>311.94</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1622</v>
+      </c>
+      <c r="L66" t="n">
+        <v>106</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.776</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:25.014</t>
+          <t>2026-05-29 09:37:41.665</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779421827161</v>
+        <v>1780022260215</v>
       </c>
       <c r="C67" t="n">
-        <v>86351</v>
+        <v>86809</v>
       </c>
       <c r="D67" t="n">
-        <v>837.8099999999999</v>
+        <v>266.82</v>
       </c>
       <c r="E67" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F67" t="n">
-        <v>726</v>
+        <v>759</v>
       </c>
       <c r="G67" t="n">
-        <v>76.33</v>
+        <v>311.94</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1449</v>
+      </c>
+      <c r="L67" t="n">
+        <v>105</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.622</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:25.290</t>
+          <t>2026-05-29 09:37:41.677</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779421827362</v>
+        <v>1780022260434</v>
       </c>
       <c r="C68" t="n">
-        <v>86106</v>
+        <v>85390</v>
       </c>
       <c r="D68" t="n">
-        <v>550.92</v>
+        <v>-1165.52</v>
       </c>
       <c r="E68" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F68" t="n">
-        <v>726</v>
+        <v>759</v>
       </c>
       <c r="G68" t="n">
-        <v>76.33</v>
+        <v>311.94</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1241</v>
+      </c>
+      <c r="L68" t="n">
+        <v>117</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.053</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:25.690</t>
+          <t>2026-05-29 09:37:41.716</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779421827563</v>
+        <v>1780022260634</v>
       </c>
       <c r="C69" t="n">
-        <v>86255</v>
+        <v>85269</v>
       </c>
       <c r="D69" t="n">
-        <v>672.37</v>
+        <v>-1228.24</v>
       </c>
       <c r="E69" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F69" t="n">
-        <v>726</v>
+        <v>759</v>
       </c>
       <c r="G69" t="n">
-        <v>76.33</v>
+        <v>311.94</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1080</v>
+      </c>
+      <c r="L69" t="n">
+        <v>107</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.447</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:25.692</t>
+          <t>2026-05-29 09:37:41.869</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779421827765</v>
+        <v>1780022260834</v>
       </c>
       <c r="C70" t="n">
-        <v>86430</v>
+        <v>86377</v>
       </c>
       <c r="D70" t="n">
-        <v>813.75</v>
+        <v>-58.83</v>
       </c>
       <c r="E70" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F70" t="n">
-        <v>886</v>
+        <v>759</v>
       </c>
       <c r="G70" t="n">
-        <v>84.16</v>
+        <v>311.94</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1034</v>
+      </c>
+      <c r="L70" t="n">
+        <v>106</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.618</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:26.125</t>
+          <t>2026-05-29 09:37:41.895</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779421827966</v>
+        <v>1780022261034</v>
       </c>
       <c r="C71" t="n">
-        <v>85995</v>
+        <v>85713</v>
       </c>
       <c r="D71" t="n">
-        <v>338.07</v>
+        <v>-719.89</v>
       </c>
       <c r="E71" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F71" t="n">
-        <v>886</v>
+        <v>759</v>
       </c>
       <c r="G71" t="n">
-        <v>84.16</v>
+        <v>311.94</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J71" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K71" t="n">
+        <v>860</v>
+      </c>
+      <c r="L71" t="n">
+        <v>106</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.968</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:26.126</t>
+          <t>2026-05-29 09:37:42.255</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779421828168</v>
+        <v>1780022261234</v>
       </c>
       <c r="C72" t="n">
-        <v>86040</v>
+        <v>86724</v>
       </c>
       <c r="D72" t="n">
-        <v>366.16</v>
+        <v>327.1</v>
       </c>
       <c r="E72" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F72" t="n">
-        <v>886</v>
+        <v>759</v>
       </c>
       <c r="G72" t="n">
-        <v>84.16</v>
+        <v>311.94</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1021</v>
+      </c>
+      <c r="L72" t="n">
+        <v>110</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.705</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:26.602</t>
+          <t>2026-05-29 09:37:42.265</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779421828369</v>
+        <v>1780022261434</v>
       </c>
       <c r="C73" t="n">
-        <v>86153</v>
+        <v>86508</v>
       </c>
       <c r="D73" t="n">
-        <v>460.86</v>
+        <v>94.75</v>
       </c>
       <c r="E73" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F73" t="n">
-        <v>886</v>
+        <v>759</v>
       </c>
       <c r="G73" t="n">
-        <v>84.16</v>
+        <v>311.94</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K73" t="n">
+        <v>829</v>
+      </c>
+      <c r="L73" t="n">
+        <v>113</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.509</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:26.602</t>
+          <t>2026-05-29 09:37:42.614</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779421828570</v>
+        <v>1780022261634</v>
       </c>
       <c r="C74" t="n">
-        <v>86327</v>
+        <v>85572</v>
       </c>
       <c r="D74" t="n">
-        <v>611.8099999999999</v>
+        <v>-845.99</v>
       </c>
       <c r="E74" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F74" t="n">
-        <v>805</v>
+        <v>759</v>
       </c>
       <c r="G74" t="n">
-        <v>83.48</v>
+        <v>311.94</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K74" t="n">
+        <v>980</v>
+      </c>
+      <c r="L74" t="n">
+        <v>108</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:26.603</t>
+          <t>2026-05-29 09:37:42.615</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779421828772</v>
+        <v>1780022261834</v>
       </c>
       <c r="C75" t="n">
-        <v>85961</v>
+        <v>86003</v>
       </c>
       <c r="D75" t="n">
-        <v>215.22</v>
+        <v>-372.69</v>
       </c>
       <c r="E75" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F75" t="n">
-        <v>805</v>
+        <v>759</v>
       </c>
       <c r="G75" t="n">
-        <v>83.48</v>
+        <v>311.94</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>781</v>
+      </c>
+      <c r="L75" t="n">
+        <v>109</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:26.917</t>
+          <t>2026-05-29 09:37:43.496</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779421828973</v>
+        <v>1780022262034</v>
       </c>
       <c r="C76" t="n">
-        <v>86160</v>
+        <v>86165</v>
       </c>
       <c r="D76" t="n">
-        <v>403.46</v>
+        <v>-192.05</v>
       </c>
       <c r="E76" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F76" t="n">
-        <v>805</v>
+        <v>759</v>
       </c>
       <c r="G76" t="n">
-        <v>83.48</v>
+        <v>311.94</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1461</v>
+      </c>
+      <c r="L76" t="n">
+        <v>108</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.031</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:26.917</t>
+          <t>2026-05-29 09:37:43.497</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779421829174</v>
+        <v>1780022262253</v>
       </c>
       <c r="C77" t="n">
-        <v>86394</v>
+        <v>85942</v>
       </c>
       <c r="D77" t="n">
-        <v>617.29</v>
+        <v>-405.45</v>
       </c>
       <c r="E77" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="F77" t="n">
-        <v>585</v>
+        <v>759</v>
       </c>
       <c r="G77" t="n">
-        <v>102.65</v>
+        <v>311.94</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1243</v>
+      </c>
+      <c r="L77" t="n">
+        <v>105</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.096</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:27.303</t>
+          <t>2026-05-29 09:37:43.498</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779421829376</v>
+        <v>1780022262453</v>
       </c>
       <c r="C78" t="n">
-        <v>86408</v>
+        <v>86185</v>
       </c>
       <c r="D78" t="n">
-        <v>600.42</v>
+        <v>-142.18</v>
       </c>
       <c r="E78" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="F78" t="n">
-        <v>585</v>
+        <v>759</v>
       </c>
       <c r="G78" t="n">
-        <v>102.65</v>
+        <v>311.94</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1045</v>
+      </c>
+      <c r="L78" t="n">
+        <v>106</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.873</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:27.304</t>
+          <t>2026-05-29 09:37:43.500</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779421829578</v>
+        <v>1780022262653</v>
       </c>
       <c r="C79" t="n">
-        <v>85980</v>
+        <v>86501</v>
       </c>
       <c r="D79" t="n">
-        <v>142.4</v>
+        <v>180.93</v>
       </c>
       <c r="E79" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="F79" t="n">
-        <v>585</v>
+        <v>3578</v>
       </c>
       <c r="G79" t="n">
-        <v>102.65</v>
+        <v>311.94</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K79" t="n">
+        <v>846</v>
+      </c>
+      <c r="L79" t="n">
+        <v>116</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.992</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:27.726</t>
+          <t>2026-05-29 09:37:43.758</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779421829779</v>
+        <v>1780022262853</v>
       </c>
       <c r="C80" t="n">
-        <v>86152</v>
+        <v>86546</v>
       </c>
       <c r="D80" t="n">
-        <v>307.28</v>
+        <v>216.88</v>
       </c>
       <c r="E80" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="F80" t="n">
-        <v>585</v>
+        <v>3578</v>
       </c>
       <c r="G80" t="n">
-        <v>102.65</v>
+        <v>311.94</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K80" t="n">
+        <v>903</v>
+      </c>
+      <c r="L80" t="n">
+        <v>117</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.811</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:27.727</t>
+          <t>2026-05-29 09:37:44.115</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779421829980</v>
+        <v>1780022263054</v>
       </c>
       <c r="C81" t="n">
-        <v>86367</v>
+        <v>86653</v>
       </c>
       <c r="D81" t="n">
-        <v>506.92</v>
+        <v>313.04</v>
       </c>
       <c r="E81" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="F81" t="n">
-        <v>585</v>
+        <v>3578</v>
       </c>
       <c r="G81" t="n">
-        <v>102.65</v>
+        <v>311.94</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1060</v>
+      </c>
+      <c r="L81" t="n">
+        <v>106</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.316</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:28.236</t>
+          <t>2026-05-29 09:37:44.117</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779421830182</v>
+        <v>1780022263253</v>
       </c>
       <c r="C82" t="n">
-        <v>85925</v>
+        <v>87104</v>
       </c>
       <c r="D82" t="n">
-        <v>39.57</v>
+        <v>748.39</v>
       </c>
       <c r="E82" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="F82" t="n">
-        <v>845</v>
+        <v>3578</v>
       </c>
       <c r="G82" t="n">
-        <v>104.34</v>
+        <v>311.94</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K82" t="n">
+        <v>863</v>
+      </c>
+      <c r="L82" t="n">
+        <v>119</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.884</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:28.260</t>
+          <t>2026-05-29 09:37:44.488</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779421830383</v>
+        <v>1780022263453</v>
       </c>
       <c r="C83" t="n">
-        <v>86037</v>
+        <v>88137</v>
       </c>
       <c r="D83" t="n">
-        <v>149.59</v>
+        <v>1743.97</v>
       </c>
       <c r="E83" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="F83" t="n">
-        <v>845</v>
+        <v>3578</v>
       </c>
       <c r="G83" t="n">
-        <v>104.34</v>
+        <v>311.94</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1034</v>
+      </c>
+      <c r="L83" t="n">
+        <v>109</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.711</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:28.999</t>
+          <t>2026-05-29 09:37:44.489</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779421830585</v>
+        <v>1780022263653</v>
       </c>
       <c r="C84" t="n">
-        <v>86145</v>
+        <v>87428</v>
       </c>
       <c r="D84" t="n">
-        <v>250.11</v>
+        <v>947.77</v>
       </c>
       <c r="E84" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="F84" t="n">
-        <v>845</v>
+        <v>3578</v>
       </c>
       <c r="G84" t="n">
-        <v>104.34</v>
+        <v>311.94</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K84" t="n">
+        <v>836</v>
+      </c>
+      <c r="L84" t="n">
+        <v>107</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.507</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:29.000</t>
+          <t>2026-05-29 09:37:45.351</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779421830786</v>
+        <v>1780022263853</v>
       </c>
       <c r="C85" t="n">
-        <v>86448</v>
+        <v>86402</v>
       </c>
       <c r="D85" t="n">
-        <v>540.61</v>
+        <v>-125.62</v>
       </c>
       <c r="E85" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="F85" t="n">
-        <v>726</v>
+        <v>3578</v>
       </c>
       <c r="G85" t="n">
-        <v>103.37</v>
+        <v>311.94</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1496</v>
+      </c>
+      <c r="L85" t="n">
+        <v>116</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.296</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:29.001</t>
+          <t>2026-05-29 09:37:45.352</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779421830987</v>
+        <v>1780022264072</v>
       </c>
       <c r="C86" t="n">
-        <v>86008</v>
+        <v>86605</v>
       </c>
       <c r="D86" t="n">
-        <v>73.58</v>
+        <v>83.66</v>
       </c>
       <c r="E86" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="F86" t="n">
-        <v>726</v>
+        <v>3578</v>
       </c>
       <c r="G86" t="n">
-        <v>103.37</v>
+        <v>311.94</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1279</v>
+      </c>
+      <c r="L86" t="n">
+        <v>112</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.309</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:29.002</t>
+          <t>2026-05-29 09:37:45.355</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779421831189</v>
+        <v>1780022264272</v>
       </c>
       <c r="C87" t="n">
-        <v>86203</v>
+        <v>85754</v>
       </c>
       <c r="D87" t="n">
-        <v>264.9</v>
+        <v>-771.52</v>
       </c>
       <c r="E87" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="F87" t="n">
-        <v>726</v>
+        <v>3578</v>
       </c>
       <c r="G87" t="n">
-        <v>103.37</v>
+        <v>311.94</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1081</v>
+      </c>
+      <c r="L87" t="n">
+        <v>111</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.587</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:29.344</t>
+          <t>2026-05-29 09:37:45.356</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779421831390</v>
+        <v>1780022264472</v>
       </c>
       <c r="C88" t="n">
-        <v>86434</v>
+        <v>85451</v>
       </c>
       <c r="D88" t="n">
-        <v>482.65</v>
+        <v>-1035.95</v>
       </c>
       <c r="E88" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="F88" t="n">
-        <v>624</v>
+        <v>3578</v>
       </c>
       <c r="G88" t="n">
-        <v>111</v>
+        <v>311.94</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K88" t="n">
+        <v>883</v>
+      </c>
+      <c r="L88" t="n">
+        <v>114</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.326</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:29.363</t>
+          <t>2026-05-29 09:37:45.790</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779421831592</v>
+        <v>1780022264672</v>
       </c>
       <c r="C89" t="n">
-        <v>86094</v>
+        <v>87270</v>
       </c>
       <c r="D89" t="n">
-        <v>118.52</v>
+        <v>834.85</v>
       </c>
       <c r="E89" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="F89" t="n">
-        <v>624</v>
+        <v>3578</v>
       </c>
       <c r="G89" t="n">
-        <v>111</v>
+        <v>311.94</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1117</v>
+      </c>
+      <c r="L89" t="n">
+        <v>117</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.848</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:30.239</t>
+          <t>2026-05-29 09:37:45.792</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779421831793</v>
+        <v>1780022264872</v>
       </c>
       <c r="C90" t="n">
-        <v>86198</v>
+        <v>86755</v>
       </c>
       <c r="D90" t="n">
-        <v>216.6</v>
+        <v>278.11</v>
       </c>
       <c r="E90" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="F90" t="n">
-        <v>624</v>
+        <v>3578</v>
       </c>
       <c r="G90" t="n">
+        <v>311.94</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K90" t="n">
+        <v>919</v>
+      </c>
+      <c r="L90" t="n">
         <v>111</v>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="M90" t="n">
+        <v>1.034</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:30.240</t>
+          <t>2026-05-29 09:37:46.128</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779421831995</v>
+        <v>1780022265072</v>
       </c>
       <c r="C91" t="n">
-        <v>86317</v>
+        <v>86529</v>
       </c>
       <c r="D91" t="n">
-        <v>324.77</v>
+        <v>38.2</v>
       </c>
       <c r="E91" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="F91" t="n">
-        <v>624</v>
+        <v>3578</v>
       </c>
       <c r="G91" t="n">
-        <v>111</v>
+        <v>311.94</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1055</v>
+      </c>
+      <c r="L91" t="n">
+        <v>119</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:30.240</t>
+          <t>2026-05-29 09:37:46.130</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779421832196</v>
+        <v>1780022265272</v>
       </c>
       <c r="C92" t="n">
-        <v>86586</v>
+        <v>87132</v>
       </c>
       <c r="D92" t="n">
-        <v>577.53</v>
+        <v>639.29</v>
       </c>
       <c r="E92" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="F92" t="n">
-        <v>745</v>
+        <v>3578</v>
       </c>
       <c r="G92" t="n">
-        <v>96.65000000000001</v>
+        <v>311.94</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K92" t="n">
+        <v>857</v>
+      </c>
+      <c r="L92" t="n">
+        <v>105</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.325</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:30.241</t>
+          <t>2026-05-29 09:37:46.967</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779421832397</v>
+        <v>1780022265473</v>
       </c>
       <c r="C93" t="n">
-        <v>86044</v>
+        <v>87188</v>
       </c>
       <c r="D93" t="n">
-        <v>6.65</v>
+        <v>663.33</v>
       </c>
       <c r="E93" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="F93" t="n">
-        <v>745</v>
+        <v>3578</v>
       </c>
       <c r="G93" t="n">
-        <v>96.65000000000001</v>
+        <v>311.94</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1493</v>
+      </c>
+      <c r="L93" t="n">
+        <v>109</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.317</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:30.596</t>
+          <t>2026-05-29 09:37:46.969</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779421832599</v>
+        <v>1780022265672</v>
       </c>
       <c r="C94" t="n">
-        <v>86255</v>
+        <v>87206</v>
       </c>
       <c r="D94" t="n">
-        <v>217.32</v>
+        <v>648.16</v>
       </c>
       <c r="E94" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="F94" t="n">
-        <v>745</v>
+        <v>3578</v>
       </c>
       <c r="G94" t="n">
-        <v>96.65000000000001</v>
+        <v>311.94</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1296</v>
+      </c>
+      <c r="L94" t="n">
+        <v>107</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.948</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:30.596</t>
+          <t>2026-05-29 09:37:46.970</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779421832800</v>
+        <v>1780022265872</v>
       </c>
       <c r="C95" t="n">
-        <v>86455</v>
+        <v>87261</v>
       </c>
       <c r="D95" t="n">
-        <v>406.45</v>
+        <v>670.75</v>
       </c>
       <c r="E95" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="F95" t="n">
-        <v>745</v>
+        <v>3578</v>
       </c>
       <c r="G95" t="n">
-        <v>96.65000000000001</v>
+        <v>311.94</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1097</v>
+      </c>
+      <c r="L95" t="n">
+        <v>108</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.928</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:30.994</t>
+          <t>2026-05-29 09:37:46.971</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779421833002</v>
+        <v>1780022266091</v>
       </c>
       <c r="C96" t="n">
-        <v>86362</v>
+        <v>86424</v>
       </c>
       <c r="D96" t="n">
-        <v>293.13</v>
+        <v>-199.78</v>
       </c>
       <c r="E96" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F96" t="n">
-        <v>745</v>
+        <v>3578</v>
       </c>
       <c r="G96" t="n">
-        <v>96.16</v>
+        <v>311.94</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K96" t="n">
+        <v>880</v>
+      </c>
+      <c r="L96" t="n">
+        <v>109</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.452</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:30.994</t>
+          <t>2026-05-29 09:37:47.609</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779421833203</v>
+        <v>1780022266291</v>
       </c>
       <c r="C97" t="n">
-        <v>86120</v>
+        <v>84583</v>
       </c>
       <c r="D97" t="n">
-        <v>36.47</v>
+        <v>-2030.79</v>
       </c>
       <c r="E97" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F97" t="n">
-        <v>745</v>
+        <v>3578</v>
       </c>
       <c r="G97" t="n">
-        <v>96.16</v>
+        <v>311.94</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1316</v>
+      </c>
+      <c r="L97" t="n">
+        <v>122</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.213</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:31.395</t>
+          <t>2026-05-29 09:37:47.610</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779421833404</v>
+        <v>1780022266491</v>
       </c>
       <c r="C98" t="n">
-        <v>86264</v>
+        <v>85244</v>
       </c>
       <c r="D98" t="n">
-        <v>178.65</v>
+        <v>-1268.25</v>
       </c>
       <c r="E98" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F98" t="n">
-        <v>745</v>
+        <v>3578</v>
       </c>
       <c r="G98" t="n">
-        <v>96.16</v>
+        <v>311.94</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1118</v>
+      </c>
+      <c r="L98" t="n">
+        <v>115</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.73</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:31.396</t>
+          <t>2026-05-29 09:37:47.958</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779421833606</v>
+        <v>1780022266691</v>
       </c>
       <c r="C99" t="n">
-        <v>86459</v>
+        <v>85886</v>
       </c>
       <c r="D99" t="n">
-        <v>364.72</v>
+        <v>-562.84</v>
       </c>
       <c r="E99" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F99" t="n">
-        <v>725</v>
+        <v>3578</v>
       </c>
       <c r="G99" t="n">
-        <v>91.09999999999999</v>
+        <v>311.94</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1266</v>
+      </c>
+      <c r="L99" t="n">
+        <v>113</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.448</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:31.824</t>
+          <t>2026-05-29 09:37:47.960</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779421833807</v>
+        <v>1780022266891</v>
       </c>
       <c r="C100" t="n">
-        <v>86022</v>
+        <v>84829</v>
       </c>
       <c r="D100" t="n">
-        <v>-90.52</v>
+        <v>-1591.7</v>
       </c>
       <c r="E100" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F100" t="n">
-        <v>725</v>
+        <v>3578</v>
       </c>
       <c r="G100" t="n">
-        <v>91.09999999999999</v>
+        <v>311.94</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1068</v>
+      </c>
+      <c r="L100" t="n">
+        <v>114</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.928</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:31.825</t>
+          <t>2026-05-29 09:37:47.962</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779421834009</v>
+        <v>1780022267091</v>
       </c>
       <c r="C101" t="n">
-        <v>86220</v>
+        <v>84578</v>
       </c>
       <c r="D101" t="n">
-        <v>112.01</v>
+        <v>-1763.11</v>
       </c>
       <c r="E101" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F101" t="n">
-        <v>725</v>
+        <v>3578</v>
       </c>
       <c r="G101" t="n">
-        <v>91.09999999999999</v>
+        <v>311.94</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K101" t="n">
+        <v>869</v>
+      </c>
+      <c r="L101" t="n">
+        <v>104</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.726</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:32.316</t>
+          <t>2026-05-29 09:37:48.262</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779421834210</v>
+        <v>1780022267291</v>
       </c>
       <c r="C102" t="n">
-        <v>86395</v>
+        <v>84543</v>
       </c>
       <c r="D102" t="n">
-        <v>281.41</v>
+        <v>-1709.96</v>
       </c>
       <c r="E102" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F102" t="n">
-        <v>725</v>
+        <v>3578</v>
       </c>
       <c r="G102" t="n">
-        <v>91.09999999999999</v>
+        <v>311.94</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K102" t="n">
+        <v>970</v>
+      </c>
+      <c r="L102" t="n">
+        <v>116</v>
+      </c>
+      <c r="M102" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:32.317</t>
+          <t>2026-05-29 09:37:48.263</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779421834411</v>
+        <v>1780022267491</v>
       </c>
       <c r="C103" t="n">
-        <v>86143</v>
+        <v>84076</v>
       </c>
       <c r="D103" t="n">
-        <v>15.34</v>
+        <v>-2091.46</v>
       </c>
       <c r="E103" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F103" t="n">
-        <v>665</v>
+        <v>3578</v>
       </c>
       <c r="G103" t="n">
-        <v>94.22</v>
+        <v>311.94</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K103" t="n">
+        <v>772</v>
+      </c>
+      <c r="L103" t="n">
+        <v>114</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.748</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:32.642</t>
+          <t>2026-05-29 09:37:48.560</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779421834613</v>
+        <v>1780022267691</v>
       </c>
       <c r="C104" t="n">
-        <v>86171</v>
+        <v>84878</v>
       </c>
       <c r="D104" t="n">
-        <v>42.57</v>
+        <v>-1184.89</v>
       </c>
       <c r="E104" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F104" t="n">
-        <v>665</v>
+        <v>3578</v>
       </c>
       <c r="G104" t="n">
-        <v>94.22</v>
+        <v>311.94</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K104" t="n">
+        <v>868</v>
+      </c>
+      <c r="L104" t="n">
+        <v>114</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.745</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:32.643</t>
+          <t>2026-05-29 09:37:49.146</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779421834814</v>
+        <v>1780022267910</v>
       </c>
       <c r="C105" t="n">
-        <v>86329</v>
+        <v>83977</v>
       </c>
       <c r="D105" t="n">
-        <v>198.44</v>
+        <v>-2026.64</v>
       </c>
       <c r="E105" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F105" t="n">
-        <v>665</v>
+        <v>3578</v>
       </c>
       <c r="G105" t="n">
-        <v>94.22</v>
+        <v>311.94</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1235</v>
+      </c>
+      <c r="L105" t="n">
+        <v>110</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.904</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:33.055</t>
+          <t>2026-05-29 09:37:49.197</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779421835016</v>
+        <v>1780022268110</v>
       </c>
       <c r="C106" t="n">
-        <v>86509</v>
+        <v>82565</v>
       </c>
       <c r="D106" t="n">
-        <v>368.52</v>
+        <v>-3337.31</v>
       </c>
       <c r="E106" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F106" t="n">
-        <v>685</v>
+        <v>3578</v>
       </c>
       <c r="G106" t="n">
-        <v>78.59999999999999</v>
+        <v>311.94</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1086</v>
+      </c>
+      <c r="L106" t="n">
+        <v>120</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1.325</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:33.056</t>
+          <t>2026-05-29 09:37:49.535</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779421835217</v>
+        <v>1780022268310</v>
       </c>
       <c r="C107" t="n">
-        <v>86004</v>
+        <v>83068</v>
       </c>
       <c r="D107" t="n">
-        <v>-154.91</v>
+        <v>-2667.45</v>
       </c>
       <c r="E107" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F107" t="n">
-        <v>685</v>
+        <v>3578</v>
       </c>
       <c r="G107" t="n">
-        <v>78.59999999999999</v>
+        <v>311.94</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1224</v>
+      </c>
+      <c r="L107" t="n">
+        <v>116</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1.646</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:33.452</t>
+          <t>2026-05-29 09:37:49.550</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779421835418</v>
+        <v>1780022268510</v>
       </c>
       <c r="C108" t="n">
-        <v>86195</v>
+        <v>83924</v>
       </c>
       <c r="D108" t="n">
-        <v>43.84</v>
+        <v>-1678.07</v>
       </c>
       <c r="E108" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F108" t="n">
-        <v>685</v>
+        <v>3578</v>
       </c>
       <c r="G108" t="n">
-        <v>78.59999999999999</v>
+        <v>311.94</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1039</v>
+      </c>
+      <c r="L108" t="n">
+        <v>109</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1.043</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:33.489</t>
+          <t>2026-05-29 09:37:49.554</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779421835620</v>
+        <v>1780022268710</v>
       </c>
       <c r="C109" t="n">
-        <v>86360</v>
+        <v>84673</v>
       </c>
       <c r="D109" t="n">
-        <v>206.65</v>
+        <v>-845.17</v>
       </c>
       <c r="E109" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F109" t="n">
-        <v>685</v>
+        <v>3578</v>
       </c>
       <c r="G109" t="n">
-        <v>78.59999999999999</v>
+        <v>311.94</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K109" t="n">
+        <v>843</v>
+      </c>
+      <c r="L109" t="n">
+        <v>108</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.477</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:34.175</t>
+          <t>2026-05-29 09:37:49.924</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779421835821</v>
+        <v>1780022268910</v>
       </c>
       <c r="C110" t="n">
-        <v>86583</v>
+        <v>84025</v>
       </c>
       <c r="D110" t="n">
-        <v>419.31</v>
+        <v>-1450.91</v>
       </c>
       <c r="E110" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F110" t="n">
-        <v>785</v>
+        <v>3578</v>
       </c>
       <c r="G110" t="n">
-        <v>76.28</v>
+        <v>311.94</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1013</v>
+      </c>
+      <c r="L110" t="n">
+        <v>114</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.277</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:34.176</t>
+          <t>2026-05-29 09:37:49.925</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779421836023</v>
+        <v>1780022269110</v>
       </c>
       <c r="C111" t="n">
-        <v>86032</v>
+        <v>84157</v>
       </c>
       <c r="D111" t="n">
-        <v>-152.65</v>
+        <v>-1246.37</v>
       </c>
       <c r="E111" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F111" t="n">
-        <v>785</v>
+        <v>3578</v>
       </c>
       <c r="G111" t="n">
-        <v>76.28</v>
+        <v>311.94</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K111" t="n">
+        <v>815</v>
+      </c>
+      <c r="L111" t="n">
+        <v>113</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.514</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:34.176</t>
+          <t>2026-05-29 09:37:50.310</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779421836224</v>
+        <v>1780022269310</v>
       </c>
       <c r="C112" t="n">
-        <v>86198</v>
+        <v>83721</v>
       </c>
       <c r="D112" t="n">
-        <v>20.98</v>
+        <v>-1620.05</v>
       </c>
       <c r="E112" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F112" t="n">
-        <v>785</v>
+        <v>3578</v>
       </c>
       <c r="G112" t="n">
-        <v>76.28</v>
+        <v>311.94</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K112" t="n">
+        <v>999</v>
+      </c>
+      <c r="L112" t="n">
+        <v>118</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.741</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:34.177</t>
+          <t>2026-05-29 09:37:50.346</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779421836425</v>
+        <v>1780022269510</v>
       </c>
       <c r="C113" t="n">
-        <v>86318</v>
+        <v>83574</v>
       </c>
       <c r="D113" t="n">
-        <v>139.93</v>
+        <v>-1686.05</v>
       </c>
       <c r="E113" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F113" t="n">
-        <v>785</v>
+        <v>3578</v>
       </c>
       <c r="G113" t="n">
-        <v>76.28</v>
+        <v>311.94</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K113" t="n">
+        <v>835</v>
+      </c>
+      <c r="L113" t="n">
+        <v>105</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:34.480</t>
+          <t>2026-05-29 09:37:50.949</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779421836627</v>
+        <v>1780022269710</v>
       </c>
       <c r="C114" t="n">
-        <v>86497</v>
+        <v>83918</v>
       </c>
       <c r="D114" t="n">
+        <v>-1257.74</v>
+      </c>
+      <c r="E114" t="n">
+        <v>55</v>
+      </c>
+      <c r="F114" t="n">
+        <v>3578</v>
+      </c>
+      <c r="G114" t="n">
         <v>311.94</v>
       </c>
-      <c r="E114" t="n">
-        <v>80</v>
-      </c>
-      <c r="F114" t="n">
-        <v>846</v>
-      </c>
-      <c r="G114" t="n">
-        <v>72.15000000000001</v>
-      </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1239</v>
+      </c>
+      <c r="L114" t="n">
+        <v>114</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:34.887</t>
+          <t>2026-05-29 09:37:50.981</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779421836828</v>
+        <v>1780022269929</v>
       </c>
       <c r="C115" t="n">
-        <v>86012</v>
+        <v>84208</v>
       </c>
       <c r="D115" t="n">
-        <v>-188.66</v>
+        <v>-904.86</v>
       </c>
       <c r="E115" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F115" t="n">
-        <v>846</v>
+        <v>7217</v>
       </c>
       <c r="G115" t="n">
-        <v>72.15000000000001</v>
+        <v>311.94</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1051</v>
+      </c>
+      <c r="L115" t="n">
+        <v>111</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.948</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:34.888</t>
+          <t>2026-05-29 09:37:51.115</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779421837030</v>
+        <v>1780022270129</v>
       </c>
       <c r="C116" t="n">
-        <v>86221</v>
+        <v>84237</v>
       </c>
       <c r="D116" t="n">
-        <v>29.77</v>
+        <v>-830.61</v>
       </c>
       <c r="E116" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F116" t="n">
-        <v>846</v>
+        <v>7217</v>
       </c>
       <c r="G116" t="n">
-        <v>72.15000000000001</v>
+        <v>311.94</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K116" t="n">
+        <v>985</v>
+      </c>
+      <c r="L116" t="n">
+        <v>118</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.879</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:35.312</t>
+          <t>2026-05-29 09:37:51.119</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779421837231</v>
+        <v>1780022270329</v>
       </c>
       <c r="C117" t="n">
-        <v>86416</v>
+        <v>84787</v>
       </c>
       <c r="D117" t="n">
-        <v>223.28</v>
+        <v>-239.08</v>
       </c>
       <c r="E117" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F117" t="n">
-        <v>846</v>
+        <v>7217</v>
       </c>
       <c r="G117" t="n">
-        <v>72.15000000000001</v>
+        <v>311.94</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K117" t="n">
+        <v>789</v>
+      </c>
+      <c r="L117" t="n">
+        <v>112</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.964</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:35.312</t>
+          <t>2026-05-29 09:37:51.932</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779421837433</v>
+        <v>1780022270529</v>
       </c>
       <c r="C118" t="n">
-        <v>86264</v>
+        <v>84687</v>
       </c>
       <c r="D118" t="n">
-        <v>60.12</v>
+        <v>-327.13</v>
       </c>
       <c r="E118" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F118" t="n">
-        <v>705</v>
+        <v>7217</v>
       </c>
       <c r="G118" t="n">
-        <v>62.22</v>
+        <v>311.94</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1402</v>
+      </c>
+      <c r="L118" t="n">
+        <v>112</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.956</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:35.818</t>
+          <t>2026-05-29 09:37:51.933</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779421837634</v>
+        <v>1780022270729</v>
       </c>
       <c r="C119" t="n">
-        <v>86144</v>
+        <v>84569</v>
       </c>
       <c r="D119" t="n">
-        <v>-62.89</v>
+        <v>-428.77</v>
       </c>
       <c r="E119" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F119" t="n">
-        <v>705</v>
+        <v>7217</v>
       </c>
       <c r="G119" t="n">
-        <v>62.22</v>
+        <v>311.94</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1203</v>
+      </c>
+      <c r="L119" t="n">
+        <v>107</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.862</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:51.934</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1780022270929</v>
+      </c>
+      <c r="C120" t="n">
+        <v>84152</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-824.33</v>
+      </c>
+      <c r="E120" t="n">
+        <v>55</v>
+      </c>
+      <c r="F120" t="n">
+        <v>7217</v>
+      </c>
+      <c r="G120" t="n">
+        <v>311.94</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1004</v>
+      </c>
+      <c r="L120" t="n">
+        <v>108</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.905</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:51.935</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1780022271129</v>
+      </c>
+      <c r="C121" t="n">
+        <v>85086</v>
+      </c>
+      <c r="D121" t="n">
+        <v>150.88</v>
+      </c>
+      <c r="E121" t="n">
+        <v>55</v>
+      </c>
+      <c r="F121" t="n">
+        <v>7217</v>
+      </c>
+      <c r="G121" t="n">
+        <v>311.94</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K121" t="n">
+        <v>805</v>
+      </c>
+      <c r="L121" t="n">
+        <v>102</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.906</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:52.179</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1780022271329</v>
+      </c>
+      <c r="C122" t="n">
+        <v>84421</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-521.66</v>
+      </c>
+      <c r="E122" t="n">
+        <v>54</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1379</v>
+      </c>
+      <c r="G122" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K122" t="n">
+        <v>850</v>
+      </c>
+      <c r="L122" t="n">
+        <v>117</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.472</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:52.547</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1780022271529</v>
+      </c>
+      <c r="C123" t="n">
+        <v>83989</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-927.58</v>
+      </c>
+      <c r="E123" t="n">
+        <v>54</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1379</v>
+      </c>
+      <c r="G123" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1017</v>
+      </c>
+      <c r="L123" t="n">
+        <v>121</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1.058</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:52.548</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1780022271729</v>
+      </c>
+      <c r="C124" t="n">
+        <v>83695</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-1175.2</v>
+      </c>
+      <c r="E124" t="n">
+        <v>54</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1379</v>
+      </c>
+      <c r="G124" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K124" t="n">
+        <v>818</v>
+      </c>
+      <c r="L124" t="n">
+        <v>113</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1.055</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:53.038</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1780022271929</v>
+      </c>
+      <c r="C125" t="n">
+        <v>83892</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-919.4400000000001</v>
+      </c>
+      <c r="E125" t="n">
+        <v>54</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1379</v>
+      </c>
+      <c r="G125" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1108</v>
+      </c>
+      <c r="L125" t="n">
+        <v>116</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.764</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:53.040</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1780022272148</v>
+      </c>
+      <c r="C126" t="n">
+        <v>83397</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-1368.47</v>
+      </c>
+      <c r="E126" t="n">
+        <v>54</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1379</v>
+      </c>
+      <c r="G126" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K126" t="n">
+        <v>891</v>
+      </c>
+      <c r="L126" t="n">
+        <v>112</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1.081</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:53.271</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1780022272348</v>
+      </c>
+      <c r="C127" t="n">
+        <v>83580</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-1117.04</v>
+      </c>
+      <c r="E127" t="n">
+        <v>54</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1379</v>
+      </c>
+      <c r="G127" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K127" t="n">
+        <v>921</v>
+      </c>
+      <c r="L127" t="n">
+        <v>122</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1.071</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:53.272</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1780022272548</v>
+      </c>
+      <c r="C128" t="n">
+        <v>83515</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-1126.19</v>
+      </c>
+      <c r="E128" t="n">
+        <v>54</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1379</v>
+      </c>
+      <c r="G128" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K128" t="n">
+        <v>723</v>
+      </c>
+      <c r="L128" t="n">
+        <v>108</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1.192</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:53.807</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1780022272748</v>
+      </c>
+      <c r="C129" t="n">
+        <v>83667</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-917.88</v>
+      </c>
+      <c r="E129" t="n">
+        <v>54</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1379</v>
+      </c>
+      <c r="G129" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1057</v>
+      </c>
+      <c r="L129" t="n">
+        <v>117</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:53.808</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1780022272948</v>
+      </c>
+      <c r="C130" t="n">
+        <v>84378</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-160.99</v>
+      </c>
+      <c r="E130" t="n">
+        <v>54</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1639</v>
+      </c>
+      <c r="G130" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K130" t="n">
+        <v>859</v>
+      </c>
+      <c r="L130" t="n">
+        <v>108</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1.063</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:54.510</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1780022273148</v>
+      </c>
+      <c r="C131" t="n">
+        <v>84152</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-378.94</v>
+      </c>
+      <c r="E131" t="n">
+        <v>54</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1639</v>
+      </c>
+      <c r="G131" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1361</v>
+      </c>
+      <c r="L131" t="n">
+        <v>115</v>
+      </c>
+      <c r="M131" t="n">
+        <v>1.058</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:54.517</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1780022273348</v>
+      </c>
+      <c r="C132" t="n">
+        <v>83910</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-601.99</v>
+      </c>
+      <c r="E132" t="n">
+        <v>54</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1639</v>
+      </c>
+      <c r="G132" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1168</v>
+      </c>
+      <c r="L132" t="n">
+        <v>114</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:55.121</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1780022273548</v>
+      </c>
+      <c r="C133" t="n">
+        <v>84271</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-210.89</v>
+      </c>
+      <c r="E133" t="n">
+        <v>54</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1639</v>
+      </c>
+      <c r="G133" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1572</v>
+      </c>
+      <c r="L133" t="n">
+        <v>116</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1.744</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:55.122</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1780022273748</v>
+      </c>
+      <c r="C134" t="n">
+        <v>84878</v>
+      </c>
+      <c r="D134" t="n">
+        <v>406.65</v>
+      </c>
+      <c r="E134" t="n">
+        <v>62</v>
+      </c>
+      <c r="F134" t="n">
+        <v>780</v>
+      </c>
+      <c r="G134" t="n">
+        <v>305.91</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1374</v>
+      </c>
+      <c r="L134" t="n">
+        <v>106</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.725</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:55.123</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1780022273948</v>
+      </c>
+      <c r="C135" t="n">
+        <v>85152</v>
+      </c>
+      <c r="D135" t="n">
+        <v>660.3200000000001</v>
+      </c>
+      <c r="E135" t="n">
+        <v>62</v>
+      </c>
+      <c r="F135" t="n">
+        <v>780</v>
+      </c>
+      <c r="G135" t="n">
+        <v>305.91</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L135" t="n">
+        <v>104</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:55.789</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1780022274167</v>
+      </c>
+      <c r="C136" t="n">
+        <v>84621</v>
+      </c>
+      <c r="D136" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="E136" t="n">
+        <v>62</v>
+      </c>
+      <c r="F136" t="n">
+        <v>780</v>
+      </c>
+      <c r="G136" t="n">
+        <v>305.91</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1621</v>
+      </c>
+      <c r="L136" t="n">
+        <v>117</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.944</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:55.838</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1780022274367</v>
+      </c>
+      <c r="C137" t="n">
+        <v>84729</v>
+      </c>
+      <c r="D137" t="n">
+        <v>199.49</v>
+      </c>
+      <c r="E137" t="n">
+        <v>62</v>
+      </c>
+      <c r="F137" t="n">
+        <v>780</v>
+      </c>
+      <c r="G137" t="n">
+        <v>305.91</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1470</v>
+      </c>
+      <c r="L137" t="n">
+        <v>111</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.627</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:55.839</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1780022274567</v>
+      </c>
+      <c r="C138" t="n">
+        <v>84730</v>
+      </c>
+      <c r="D138" t="n">
+        <v>190.51</v>
+      </c>
+      <c r="E138" t="n">
+        <v>62</v>
+      </c>
+      <c r="F138" t="n">
+        <v>780</v>
+      </c>
+      <c r="G138" t="n">
+        <v>305.91</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1271</v>
+      </c>
+      <c r="L138" t="n">
+        <v>107</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:56.109</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1780022274767</v>
+      </c>
+      <c r="C139" t="n">
+        <v>84744</v>
+      </c>
+      <c r="D139" t="n">
+        <v>194.99</v>
+      </c>
+      <c r="E139" t="n">
+        <v>65</v>
+      </c>
+      <c r="F139" t="n">
+        <v>939</v>
+      </c>
+      <c r="G139" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1341</v>
+      </c>
+      <c r="L139" t="n">
+        <v>110</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.835</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:56.110</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1780022274967</v>
+      </c>
+      <c r="C140" t="n">
+        <v>85299</v>
+      </c>
+      <c r="D140" t="n">
+        <v>740.24</v>
+      </c>
+      <c r="E140" t="n">
+        <v>65</v>
+      </c>
+      <c r="F140" t="n">
+        <v>939</v>
+      </c>
+      <c r="G140" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1142</v>
+      </c>
+      <c r="L140" t="n">
+        <v>105</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1.134</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:56.113</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1780022275167</v>
+      </c>
+      <c r="C141" t="n">
+        <v>85596</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1000.23</v>
+      </c>
+      <c r="E141" t="n">
+        <v>65</v>
+      </c>
+      <c r="F141" t="n">
+        <v>939</v>
+      </c>
+      <c r="G141" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K141" t="n">
+        <v>945</v>
+      </c>
+      <c r="L141" t="n">
+        <v>104</v>
+      </c>
+      <c r="M141" t="n">
+        <v>1.067</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:56.826</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1780022275367</v>
+      </c>
+      <c r="C142" t="n">
+        <v>85400</v>
+      </c>
+      <c r="D142" t="n">
+        <v>754.22</v>
+      </c>
+      <c r="E142" t="n">
+        <v>65</v>
+      </c>
+      <c r="F142" t="n">
+        <v>939</v>
+      </c>
+      <c r="G142" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1457</v>
+      </c>
+      <c r="L142" t="n">
+        <v>106</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1.559</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:56.836</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1780022275567</v>
+      </c>
+      <c r="C143" t="n">
+        <v>84939</v>
+      </c>
+      <c r="D143" t="n">
+        <v>255.51</v>
+      </c>
+      <c r="E143" t="n">
+        <v>65</v>
+      </c>
+      <c r="F143" t="n">
+        <v>939</v>
+      </c>
+      <c r="G143" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1268</v>
+      </c>
+      <c r="L143" t="n">
+        <v>113</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.748</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:57.566</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1780022275767</v>
+      </c>
+      <c r="C144" t="n">
+        <v>84379</v>
+      </c>
+      <c r="D144" t="n">
+        <v>-317.27</v>
+      </c>
+      <c r="E144" t="n">
+        <v>65</v>
+      </c>
+      <c r="F144" t="n">
+        <v>939</v>
+      </c>
+      <c r="G144" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J144" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1797</v>
+      </c>
+      <c r="L144" t="n">
+        <v>118</v>
+      </c>
+      <c r="M144" t="n">
+        <v>1.441</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:57.593</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1780022275967</v>
+      </c>
+      <c r="C145" t="n">
+        <v>84288</v>
+      </c>
+      <c r="D145" t="n">
+        <v>-392.41</v>
+      </c>
+      <c r="E145" t="n">
+        <v>65</v>
+      </c>
+      <c r="F145" t="n">
+        <v>939</v>
+      </c>
+      <c r="G145" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J145" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1625</v>
+      </c>
+      <c r="L145" t="n">
+        <v>111</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1.032</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:57.594</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1780022276167</v>
+      </c>
+      <c r="C146" t="n">
+        <v>83694</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-966.79</v>
+      </c>
+      <c r="E146" t="n">
+        <v>65</v>
+      </c>
+      <c r="F146" t="n">
+        <v>939</v>
+      </c>
+      <c r="G146" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J146" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K146" t="n">
+        <v>1426</v>
+      </c>
+      <c r="L146" t="n">
+        <v>109</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.959</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:57.595</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1780022276386</v>
+      </c>
+      <c r="C147" t="n">
+        <v>83915</v>
+      </c>
+      <c r="D147" t="n">
+        <v>-697.45</v>
+      </c>
+      <c r="E147" t="n">
+        <v>65</v>
+      </c>
+      <c r="F147" t="n">
+        <v>939</v>
+      </c>
+      <c r="G147" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J147" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1208</v>
+      </c>
+      <c r="L147" t="n">
+        <v>106</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0.803</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:58.938</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1780022276586</v>
+      </c>
+      <c r="C148" t="n">
+        <v>84120</v>
+      </c>
+      <c r="D148" t="n">
+        <v>-457.57</v>
+      </c>
+      <c r="E148" t="n">
+        <v>65</v>
+      </c>
+      <c r="F148" t="n">
+        <v>939</v>
+      </c>
+      <c r="G148" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J148" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K148" t="n">
+        <v>2351</v>
+      </c>
+      <c r="L148" t="n">
+        <v>106</v>
+      </c>
+      <c r="M148" t="n">
+        <v>1.105</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:58.939</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1780022276786</v>
+      </c>
+      <c r="C149" t="n">
+        <v>83540</v>
+      </c>
+      <c r="D149" t="n">
+        <v>-1014.7</v>
+      </c>
+      <c r="E149" t="n">
+        <v>65</v>
+      </c>
+      <c r="F149" t="n">
+        <v>939</v>
+      </c>
+      <c r="G149" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J149" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K149" t="n">
+        <v>2152</v>
+      </c>
+      <c r="L149" t="n">
+        <v>117</v>
+      </c>
+      <c r="M149" t="n">
+        <v>1.155</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:58.941</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1780022276986</v>
+      </c>
+      <c r="C150" t="n">
+        <v>83483</v>
+      </c>
+      <c r="D150" t="n">
+        <v>-1020.96</v>
+      </c>
+      <c r="E150" t="n">
+        <v>65</v>
+      </c>
+      <c r="F150" t="n">
+        <v>939</v>
+      </c>
+      <c r="G150" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J150" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1954</v>
+      </c>
+      <c r="L150" t="n">
+        <v>112</v>
+      </c>
+      <c r="M150" t="n">
+        <v>1.277</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:58.943</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1780022277187</v>
+      </c>
+      <c r="C151" t="n">
+        <v>83594</v>
+      </c>
+      <c r="D151" t="n">
+        <v>-858.91</v>
+      </c>
+      <c r="E151" t="n">
+        <v>65</v>
+      </c>
+      <c r="F151" t="n">
+        <v>939</v>
+      </c>
+      <c r="G151" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="J151" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1754</v>
+      </c>
+      <c r="L151" t="n">
+        <v>107</v>
+      </c>
+      <c r="M151" t="n">
+        <v>1.286</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:58.944</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1780022277406</v>
+      </c>
+      <c r="C152" t="n">
+        <v>83448</v>
+      </c>
+      <c r="D152" t="n">
+        <v>-961.97</v>
+      </c>
+      <c r="E152" t="n">
+        <v>65</v>
+      </c>
+      <c r="F152" t="n">
+        <v>939</v>
+      </c>
+      <c r="G152" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J152" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K152" t="n">
+        <v>1537</v>
+      </c>
+      <c r="L152" t="n">
+        <v>113</v>
+      </c>
+      <c r="M152" t="n">
+        <v>1.148</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:58.945</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1780022277606</v>
+      </c>
+      <c r="C153" t="n">
+        <v>83507</v>
+      </c>
+      <c r="D153" t="n">
+        <v>-854.87</v>
+      </c>
+      <c r="E153" t="n">
+        <v>65</v>
+      </c>
+      <c r="F153" t="n">
+        <v>939</v>
+      </c>
+      <c r="G153" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J153" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1338</v>
+      </c>
+      <c r="L153" t="n">
+        <v>103</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1.233</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:37:58.947</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1780022277806</v>
+      </c>
+      <c r="C154" t="n">
+        <v>83740</v>
+      </c>
+      <c r="D154" t="n">
+        <v>-579.13</v>
+      </c>
+      <c r="E154" t="n">
+        <v>65</v>
+      </c>
+      <c r="F154" t="n">
+        <v>939</v>
+      </c>
+      <c r="G154" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J154" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K154" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L154" t="n">
+        <v>114</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0.974</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:38:01.869</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1780022278006</v>
+      </c>
+      <c r="C155" t="n">
+        <v>83560</v>
+      </c>
+      <c r="D155" t="n">
+        <v>-730.17</v>
+      </c>
+      <c r="E155" t="n">
+        <v>65</v>
+      </c>
+      <c r="F155" t="n">
+        <v>3259</v>
+      </c>
+      <c r="G155" t="n">
+        <v>263.94</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J155" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K155" t="n">
+        <v>3862</v>
+      </c>
+      <c r="L155" t="n">
+        <v>102</v>
+      </c>
+      <c r="M155" t="n">
+        <v>1.531</v>
       </c>
     </row>
   </sheetData>
